--- a/switch hız/switchler.xlsx
+++ b/switch hız/switchler.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,22 @@
           <t>10.133.0.98</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>12031432</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sw1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10.133.0.21</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>12031432</t>
         </is>
